--- a/templates/vacation_anomalies_template.xlsx
+++ b/templates/vacation_anomalies_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDCB1267-5A4B-4762-97C5-FC0078638154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B965B3-7D11-4797-81EE-A36A6A4D4A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="325" xr2:uid="{7F4F08CC-EE4F-4293-870C-47068A1A5ED8}"/>
+    <workbookView xWindow="3720" yWindow="3720" windowWidth="21600" windowHeight="11295" tabRatio="325" xr2:uid="{7F4F08CC-EE4F-4293-870C-47068A1A5ED8}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -310,18 +310,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -338,10 +326,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -713,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0D29666-6FE0-444B-BBC0-AD4885725B9B}">
-  <dimension ref="B2:I49"/>
+  <dimension ref="A2:I49"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
@@ -724,45 +724,45 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="2:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="3" t="s">
         <v>1</v>
       </c>
@@ -780,367 +780,393 @@
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="6"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="6"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="6"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="6"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="6"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="6"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="6"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="6"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="6"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="6"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="6"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="6"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="6"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="6"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="6"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="6"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="6"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="6"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="6"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="6"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="6"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46" s="6"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="6"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B48" s="6"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="14"/>
       <c r="C49" s="15"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="B6:H7"/>
     <mergeCell ref="B44:C44"/>
@@ -1157,32 +1183,6 @@
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/vacation_anomalies_template.xlsx
+++ b/templates/vacation_anomalies_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B965B3-7D11-4797-81EE-A36A6A4D4A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D511D08-D1CE-4143-B2C4-D3A2D6D085C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="3720" windowWidth="21600" windowHeight="11295" tabRatio="325" xr2:uid="{7F4F08CC-EE4F-4293-870C-47068A1A5ED8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="325" xr2:uid="{7F4F08CC-EE4F-4293-870C-47068A1A5ED8}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +149,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -299,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -343,12 +351,40 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -782,7 +818,7 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="12"/>
       <c r="C10" s="13"/>
-      <c r="D10" s="4"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -791,7 +827,7 @@
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="12"/>
       <c r="C11" s="13"/>
-      <c r="D11" s="4"/>
+      <c r="D11" s="16"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -800,7 +836,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="12"/>
       <c r="C12" s="13"/>
-      <c r="D12" s="4"/>
+      <c r="D12" s="16"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -809,7 +845,7 @@
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="12"/>
       <c r="C13" s="13"/>
-      <c r="D13" s="4"/>
+      <c r="D13" s="16"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -818,7 +854,7 @@
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="12"/>
       <c r="C14" s="13"/>
-      <c r="D14" s="4"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -827,7 +863,7 @@
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="12"/>
       <c r="C15" s="13"/>
-      <c r="D15" s="4"/>
+      <c r="D15" s="16"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -836,7 +872,7 @@
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="12"/>
       <c r="C16" s="13"/>
-      <c r="D16" s="4"/>
+      <c r="D16" s="16"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -845,7 +881,7 @@
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="12"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="4"/>
+      <c r="D17" s="16"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -854,7 +890,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="12"/>
       <c r="C18" s="13"/>
-      <c r="D18" s="4"/>
+      <c r="D18" s="16"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -863,7 +899,7 @@
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="12"/>
       <c r="C19" s="13"/>
-      <c r="D19" s="4"/>
+      <c r="D19" s="16"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -872,7 +908,7 @@
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="12"/>
       <c r="C20" s="13"/>
-      <c r="D20" s="4"/>
+      <c r="D20" s="16"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -881,7 +917,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="12"/>
       <c r="C21" s="13"/>
-      <c r="D21" s="4"/>
+      <c r="D21" s="16"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -890,7 +926,7 @@
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="12"/>
       <c r="C22" s="13"/>
-      <c r="D22" s="4"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -899,7 +935,7 @@
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="12"/>
       <c r="C23" s="13"/>
-      <c r="D23" s="4"/>
+      <c r="D23" s="16"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -908,7 +944,7 @@
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="12"/>
       <c r="C24" s="13"/>
-      <c r="D24" s="4"/>
+      <c r="D24" s="16"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -917,7 +953,7 @@
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="12"/>
       <c r="C25" s="13"/>
-      <c r="D25" s="4"/>
+      <c r="D25" s="16"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
@@ -926,7 +962,7 @@
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="12"/>
       <c r="C26" s="13"/>
-      <c r="D26" s="4"/>
+      <c r="D26" s="16"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -935,7 +971,7 @@
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="12"/>
       <c r="C27" s="13"/>
-      <c r="D27" s="4"/>
+      <c r="D27" s="16"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -944,7 +980,7 @@
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="12"/>
       <c r="C28" s="13"/>
-      <c r="D28" s="4"/>
+      <c r="D28" s="16"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -953,7 +989,7 @@
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="12"/>
       <c r="C29" s="13"/>
-      <c r="D29" s="4"/>
+      <c r="D29" s="16"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -962,7 +998,7 @@
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="12"/>
       <c r="C30" s="13"/>
-      <c r="D30" s="4"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -971,7 +1007,7 @@
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="12"/>
       <c r="C31" s="13"/>
-      <c r="D31" s="4"/>
+      <c r="D31" s="16"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -980,7 +1016,7 @@
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="12"/>
       <c r="C32" s="13"/>
-      <c r="D32" s="4"/>
+      <c r="D32" s="16"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
@@ -989,7 +1025,7 @@
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="12"/>
       <c r="C33" s="13"/>
-      <c r="D33" s="4"/>
+      <c r="D33" s="16"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -998,7 +1034,7 @@
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="12"/>
       <c r="C34" s="13"/>
-      <c r="D34" s="4"/>
+      <c r="D34" s="16"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -1007,7 +1043,7 @@
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="12"/>
       <c r="C35" s="13"/>
-      <c r="D35" s="4"/>
+      <c r="D35" s="16"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
@@ -1016,7 +1052,7 @@
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="12"/>
       <c r="C36" s="13"/>
-      <c r="D36" s="4"/>
+      <c r="D36" s="16"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
@@ -1025,7 +1061,7 @@
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="12"/>
       <c r="C37" s="13"/>
-      <c r="D37" s="4"/>
+      <c r="D37" s="16"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
@@ -1034,7 +1070,7 @@
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="12"/>
       <c r="C38" s="13"/>
-      <c r="D38" s="4"/>
+      <c r="D38" s="16"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
@@ -1043,7 +1079,7 @@
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="12"/>
       <c r="C39" s="13"/>
-      <c r="D39" s="4"/>
+      <c r="D39" s="16"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
@@ -1052,7 +1088,7 @@
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="12"/>
       <c r="C40" s="13"/>
-      <c r="D40" s="4"/>
+      <c r="D40" s="16"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
@@ -1061,7 +1097,7 @@
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="12"/>
       <c r="C41" s="13"/>
-      <c r="D41" s="4"/>
+      <c r="D41" s="16"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
@@ -1070,7 +1106,7 @@
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="12"/>
       <c r="C42" s="13"/>
-      <c r="D42" s="4"/>
+      <c r="D42" s="16"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -1079,7 +1115,7 @@
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="12"/>
       <c r="C43" s="13"/>
-      <c r="D43" s="4"/>
+      <c r="D43" s="16"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -1088,7 +1124,7 @@
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B44" s="12"/>
       <c r="C44" s="13"/>
-      <c r="D44" s="4"/>
+      <c r="D44" s="16"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -1097,7 +1133,7 @@
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B45" s="12"/>
       <c r="C45" s="13"/>
-      <c r="D45" s="4"/>
+      <c r="D45" s="16"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
@@ -1106,7 +1142,7 @@
     <row r="46" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B46" s="12"/>
       <c r="C46" s="13"/>
-      <c r="D46" s="4"/>
+      <c r="D46" s="16"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
@@ -1115,7 +1151,7 @@
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B47" s="12"/>
       <c r="C47" s="13"/>
-      <c r="D47" s="4"/>
+      <c r="D47" s="16"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
@@ -1124,7 +1160,7 @@
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B48" s="12"/>
       <c r="C48" s="13"/>
-      <c r="D48" s="4"/>
+      <c r="D48" s="16"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -1133,7 +1169,7 @@
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="14"/>
       <c r="C49" s="15"/>
-      <c r="D49" s="5"/>
+      <c r="D49" s="17"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -1185,8 +1221,33 @@
     <mergeCell ref="B36:C36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="H10:H49">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{913DBBC9-D456-4DFA-A976-F4E584A2265E}">
+            <xm:f>NOT(ISERROR(SEARCH("VERIFICAÇÃO",H10)))</xm:f>
+            <xm:f>"VERIFICAÇÃO"</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <i val="0"/>
+                <color rgb="FFFF0000"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>H10:H49</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/templates/vacation_anomalies_template.xlsx
+++ b/templates/vacation_anomalies_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D511D08-D1CE-4143-B2C4-D3A2D6D085C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDCB1267-5A4B-4762-97C5-FC0078638154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="325" xr2:uid="{7F4F08CC-EE4F-4293-870C-47068A1A5ED8}"/>
   </bookViews>
@@ -81,7 +81,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,14 +149,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -307,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -318,6 +310,18 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -334,57 +338,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -749,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0D29666-6FE0-444B-BBC0-AD4885725B9B}">
-  <dimension ref="A2:I49"/>
+  <dimension ref="B2:I49"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
@@ -760,45 +724,45 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
     </row>
     <row r="8" spans="2:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="11"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="3" t="s">
         <v>1</v>
       </c>
@@ -816,393 +780,367 @@
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="12"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="12"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="12"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="12"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="12"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="12"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="12"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="12"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="12"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="12"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="12"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="12"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="12"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="12"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="12"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="12"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="12"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="12"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46" s="12"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="12"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="14"/>
       <c r="C49" s="15"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="B6:H7"/>
     <mergeCell ref="B44:C44"/>
@@ -1219,35 +1157,36 @@
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="H10:H49">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{913DBBC9-D456-4DFA-A976-F4E584A2265E}">
-            <xm:f>NOT(ISERROR(SEARCH("VERIFICAÇÃO",H10)))</xm:f>
-            <xm:f>"VERIFICAÇÃO"</xm:f>
-            <x14:dxf>
-              <font>
-                <b/>
-                <i val="0"/>
-                <color rgb="FFFF0000"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>H10:H49</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
--- a/templates/vacation_anomalies_template.xlsx
+++ b/templates/vacation_anomalies_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDCB1267-5A4B-4762-97C5-FC0078638154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D511D08-D1CE-4143-B2C4-D3A2D6D085C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="325" xr2:uid="{7F4F08CC-EE4F-4293-870C-47068A1A5ED8}"/>
   </bookViews>
@@ -81,7 +81,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +149,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -299,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -310,18 +318,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -338,17 +334,57 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -713,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0D29666-6FE0-444B-BBC0-AD4885725B9B}">
-  <dimension ref="B2:I49"/>
+  <dimension ref="A2:I49"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
@@ -724,45 +760,45 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="2:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="2:8" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="3" t="s">
         <v>1</v>
       </c>
@@ -780,367 +816,393 @@
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="6"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="6"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="6"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="6"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="6"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="6"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="6"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="6"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="6"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="6"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="6"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="6"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="6"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="6"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="6"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="6"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="6"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="6"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="6"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="6"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="6"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46" s="6"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="6"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B48" s="6"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="14"/>
       <c r="C49" s="15"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="B6:H7"/>
     <mergeCell ref="B44:C44"/>
@@ -1157,36 +1219,35 @@
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="H10:H49">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{913DBBC9-D456-4DFA-A976-F4E584A2265E}">
+            <xm:f>NOT(ISERROR(SEARCH("VERIFICAÇÃO",H10)))</xm:f>
+            <xm:f>"VERIFICAÇÃO"</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <i val="0"/>
+                <color rgb="FFFF0000"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>H10:H49</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>